--- a/multiSchoolOutput/01_School_of_Engineering/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/01_School_of_Engineering/solution_weeks_9_10.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0005_02_2.01</t>
+          <t>0210_-1_B.51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0005_02_2.01</t>
+          <t>0210_-1_B.51</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,12 +3385,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0210_-1_B.51</t>
+          <t>0005_01_1.01</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0219_00_G.01</t>
+          <t>0254_01_1.08</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0209_-1_B.Z28</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7167,12 +7167,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7777,12 +7777,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7960,12 +7960,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8387,12 +8387,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8692,12 +8692,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0005_01_1.01</t>
+          <t>0005_02_2.01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9485,12 +9485,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9973,12 +9973,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10217,12 +10217,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0311_01_1.26</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11069,12 +11069,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11313,12 +11313,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11618,12 +11618,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">

--- a/multiSchoolOutput/01_School_of_Engineering/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/01_School_of_Engineering/solution_weeks_9_10.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,7 +508,7 @@
         <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0209_-1_B.Z28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -874,7 +874,7 @@
         <v>84</v>
       </c>
       <c r="F8" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0005_01_1.01</t>
+          <t>0210_-1_B.51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0210_-1_B.51</t>
+          <t>0005_02_2.01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0005_01_1.01</t>
+          <t>0005_02_2.01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2017,7 +2017,7 @@
         <v>30</v>
       </c>
       <c r="F27" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2076,7 +2076,7 @@
         <v>30</v>
       </c>
       <c r="F28" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2253,7 +2253,7 @@
         <v>80</v>
       </c>
       <c r="F31" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0003_03_3.01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2489,7 +2489,7 @@
         <v>25</v>
       </c>
       <c r="F35" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>80</v>
       </c>
       <c r="F36" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2592,12 +2592,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2609,7 +2609,7 @@
         <v>80</v>
       </c>
       <c r="F37" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2653,12 +2653,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2670,7 +2670,7 @@
         <v>50</v>
       </c>
       <c r="F38" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3036,7 +3036,7 @@
         <v>80</v>
       </c>
       <c r="F44" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3080,12 +3080,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3097,7 +3097,7 @@
         <v>30</v>
       </c>
       <c r="F45" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3219,7 +3219,7 @@
         <v>90</v>
       </c>
       <c r="F47" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3263,12 +3263,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0210_-1_B.51</t>
+          <t>0005_01_1.01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,12 +3385,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3463,7 +3463,7 @@
         <v>50</v>
       </c>
       <c r="F51" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3646,7 +3646,7 @@
         <v>30</v>
       </c>
       <c r="F54" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0008_03_3.454</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3829,7 +3829,7 @@
         <v>80</v>
       </c>
       <c r="F57" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0201_02_2.12</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3890,7 +3890,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4073,7 +4073,7 @@
         <v>90</v>
       </c>
       <c r="F61" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4117,12 +4117,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4134,7 +4134,7 @@
         <v>120</v>
       </c>
       <c r="F62" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4256,7 +4256,7 @@
         <v>120</v>
       </c>
       <c r="F64" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0005_01_1.01</t>
+          <t>0005_02_2.01</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4361,12 +4361,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0254_01_1.08</t>
+          <t>0001_02_2.347</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0005_01_1.01</t>
+          <t>0210_-1_B.51</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0300_00_NG.02</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4561,7 +4561,7 @@
         <v>30</v>
       </c>
       <c r="F69" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0300_00_NG.01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4622,7 +4622,7 @@
         <v>35</v>
       </c>
       <c r="F70" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4666,12 +4666,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0313_00_G.10</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4683,7 +4683,7 @@
         <v>35</v>
       </c>
       <c r="F71" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0008_02_2.365</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5415,7 +5415,7 @@
         <v>15</v>
       </c>
       <c r="F83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5459,12 +5459,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0311_01_1.26</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0228_-1_LG.10</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5537,7 +5537,7 @@
         <v>30</v>
       </c>
       <c r="F85" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5581,12 +5581,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0201_02_2.14</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5598,7 +5598,7 @@
         <v>50</v>
       </c>
       <c r="F86" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5903,7 +5903,7 @@
         <v>80</v>
       </c>
       <c r="F91" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6086,7 +6086,7 @@
         <v>80</v>
       </c>
       <c r="F94" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0008_-1_B.157</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6391,7 +6391,7 @@
         <v>25</v>
       </c>
       <c r="F99" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6757,7 +6757,7 @@
         <v>50</v>
       </c>
       <c r="F105" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6818,7 +6818,7 @@
         <v>80</v>
       </c>
       <c r="F106" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6862,12 +6862,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7167,12 +7167,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0201_02_2.11</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7489,7 +7489,7 @@
         <v>25</v>
       </c>
       <c r="F117" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0001_02_2.345</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7611,7 +7611,7 @@
         <v>15</v>
       </c>
       <c r="F119" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7777,12 +7777,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7899,12 +7899,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7916,7 +7916,7 @@
         <v>120</v>
       </c>
       <c r="F124" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -7960,12 +7960,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8387,12 +8387,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8692,12 +8692,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0005_02_2.01</t>
+          <t>0005_01_1.01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8892,7 +8892,7 @@
         <v>30</v>
       </c>
       <c r="F140" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9075,7 +9075,7 @@
         <v>90</v>
       </c>
       <c r="F143" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -9119,12 +9119,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9136,7 +9136,7 @@
         <v>50</v>
       </c>
       <c r="F144" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0005_01_1.01</t>
+          <t>0005_02_2.01</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9380,7 +9380,7 @@
         <v>50</v>
       </c>
       <c r="F148" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9485,12 +9485,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0228_11_11.10</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9807,7 +9807,7 @@
         <v>35</v>
       </c>
       <c r="F155" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9973,12 +9973,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0113_01_1.434</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -9990,7 +9990,7 @@
         <v>25</v>
       </c>
       <c r="F158" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10156,12 +10156,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10173,7 +10173,7 @@
         <v>80</v>
       </c>
       <c r="F161" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -10217,12 +10217,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0008_-1_B.157</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10234,7 +10234,7 @@
         <v>25</v>
       </c>
       <c r="F162" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10356,7 +10356,7 @@
         <v>30</v>
       </c>
       <c r="F164" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10478,7 +10478,7 @@
         <v>30</v>
       </c>
       <c r="F166" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10600,7 +10600,7 @@
         <v>80</v>
       </c>
       <c r="F168" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -10644,12 +10644,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10722,7 +10722,7 @@
         <v>90</v>
       </c>
       <c r="F170" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -10766,12 +10766,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0251_01_1.02</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10783,7 +10783,7 @@
         <v>25</v>
       </c>
       <c r="F171" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -10827,12 +10827,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0208_00_G.8</t>
+          <t>0335_01_1.16</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11069,12 +11069,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11208,7 +11208,7 @@
         <v>90</v>
       </c>
       <c r="F178" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -11252,12 +11252,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11313,12 +11313,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11330,7 +11330,7 @@
         <v>30</v>
       </c>
       <c r="F180" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11391,7 +11391,7 @@
         <v>90</v>
       </c>
       <c r="F181" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11618,12 +11618,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11757,7 +11757,7 @@
         <v>120</v>
       </c>
       <c r="F187" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -11801,12 +11801,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11818,7 +11818,7 @@
         <v>90</v>
       </c>
       <c r="F188" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
